--- a/Sets-DemoModels.xlsx
+++ b/Sets-DemoModels.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kristoffer\Demo_models\DemoS_012\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kristoffer\DemoS_012_timesreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B2AD92-8E72-4B4A-8FB0-D9AAB1341DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E15EBF-3D8E-43F6-B664-4A91876615C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="360" windowWidth="28800" windowHeight="15465" activeTab="1" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="2" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
     <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId2"/>
+    <sheet name="TIMESreport_Sets-Comm" sheetId="3" r:id="rId3"/>
+    <sheet name="TIMESreport_Sets-Proc" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="187">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -385,14 +387,245 @@
   </si>
   <si>
     <t>ELC*</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>TIMESReport</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>subsector</t>
+  </si>
+  <si>
+    <t>techgroup</t>
+  </si>
+  <si>
+    <t>comgroup</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Nuclear</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Renewable</t>
+  </si>
+  <si>
+    <t>TFM_Csets</t>
+  </si>
+  <si>
+    <t>TR_ELE</t>
+  </si>
+  <si>
+    <t>TR_IND</t>
+  </si>
+  <si>
+    <t>TR_MIN</t>
+  </si>
+  <si>
+    <t>TR_TRD</t>
+  </si>
+  <si>
+    <t>TR_REF</t>
+  </si>
+  <si>
+    <t>TR_AGR</t>
+  </si>
+  <si>
+    <t>TR_COM</t>
+  </si>
+  <si>
+    <t>TR_RES</t>
+  </si>
+  <si>
+    <t>TR_TRA</t>
+  </si>
+  <si>
+    <t>TR_TRM</t>
+  </si>
+  <si>
+    <t>Fossile power plants</t>
+  </si>
+  <si>
+    <t>Nuclear power plants</t>
+  </si>
+  <si>
+    <t>Renewable power plant</t>
+  </si>
+  <si>
+    <t>DMD</t>
+  </si>
+  <si>
+    <t>DIIS</t>
+  </si>
+  <si>
+    <t>Steel service</t>
+  </si>
+  <si>
+    <t>TR_ES_STEEL</t>
+  </si>
+  <si>
+    <t>Space heating</t>
+  </si>
+  <si>
+    <t>Appliances</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>DRSH,DCSH</t>
+  </si>
+  <si>
+    <t>DRAP,DCAP</t>
+  </si>
+  <si>
+    <t>TR_ES_OTH</t>
+  </si>
+  <si>
+    <t>TR_ES_APP</t>
+  </si>
+  <si>
+    <t>TR_ES_SP</t>
+  </si>
+  <si>
+    <t>DIDM1,DROT,DCOT,DAOT</t>
+  </si>
+  <si>
+    <t>Iron&amp;Stell</t>
+  </si>
+  <si>
+    <t>ITIISIN,ITIISIBF,ITIISBOF,IDMIIS</t>
+  </si>
+  <si>
+    <t>TR_STEEL</t>
+  </si>
+  <si>
+    <t>TR_PP_FOSSIL</t>
+  </si>
+  <si>
+    <t>TR_PP_NUCLEAR</t>
+  </si>
+  <si>
+    <t>TR_PP_RENEW</t>
+  </si>
+  <si>
+    <t>Mt-y</t>
+  </si>
+  <si>
+    <t>Million ton a year</t>
+  </si>
+  <si>
+    <t>TFM_Psets</t>
+  </si>
+  <si>
+    <t>EXP*,IMP*,-IMP*Z</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>NRG_OIL</t>
+  </si>
+  <si>
+    <t>NRG_COA</t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>TR_TRAPUB</t>
+  </si>
+  <si>
+    <t>Public Transport</t>
+  </si>
+  <si>
+    <t>TCAR*</t>
+  </si>
+  <si>
+    <t>TPUB*</t>
+  </si>
+  <si>
+    <t>Car transport</t>
+  </si>
+  <si>
+    <t>TR_TRACAR</t>
+  </si>
+  <si>
+    <t>TR_ES_TR</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>DTCAR,DTPUB</t>
+  </si>
+  <si>
+    <t>capacityunit</t>
+  </si>
+  <si>
+    <t>PJa</t>
+  </si>
+  <si>
+    <t>PJ annually</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>-ITIISIN,-ITIISIBF,-ITIISBOF,-IDMIIS</t>
+  </si>
+  <si>
+    <t>TR_IND,TR_AGR,TR_COM,TR_RES</t>
+  </si>
+  <si>
+    <t>000_Units</t>
+  </si>
+  <si>
+    <t>1000 units</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\Te\x\t"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -420,7 +653,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -428,17 +661,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 5" xfId="1" xr:uid="{B387DD4F-F719-4379-A4FC-680701E911D2}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -751,23 +998,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD03DB1-DD55-4548-B86E-1F92E13CF8ED}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="65.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="65.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="56" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -793,7 +1040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>72</v>
       </c>
@@ -810,7 +1057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -824,7 +1071,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -841,7 +1088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -855,7 +1102,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>79</v>
       </c>
@@ -869,7 +1116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>81</v>
       </c>
@@ -883,7 +1130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>83</v>
       </c>
@@ -905,18 +1152,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06336B7-5D6A-48EE-B122-F085391548AD}">
   <dimension ref="A1:J116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -948,7 +1195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>115</v>
@@ -972,7 +1219,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>110</v>
@@ -996,7 +1243,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>53</v>
@@ -1020,7 +1267,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -1044,7 +1291,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -1068,7 +1315,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>93</v>
@@ -1092,7 +1339,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>96</v>
@@ -1116,7 +1363,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>111</v>
@@ -1140,7 +1387,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>106</v>
@@ -1164,7 +1411,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>109</v>
@@ -1188,7 +1435,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>11</v>
@@ -1210,7 +1457,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1234,7 +1481,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1258,7 +1505,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1282,7 +1529,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -1306,7 +1553,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1330,7 +1577,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
@@ -1354,7 +1601,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
@@ -1378,7 +1625,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
@@ -1402,7 +1649,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
@@ -1426,7 +1673,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
@@ -1450,7 +1697,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>35</v>
@@ -1472,7 +1719,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -1496,7 +1743,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>37</v>
       </c>
@@ -1520,7 +1767,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
@@ -1544,7 +1791,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -1568,7 +1815,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
@@ -1592,7 +1839,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>48</v>
@@ -1614,7 +1861,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>50</v>
@@ -1636,7 +1883,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>52</v>
       </c>
@@ -1660,7 +1907,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
@@ -1684,7 +1931,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
@@ -1708,7 +1955,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>59</v>
       </c>
@@ -1732,7 +1979,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
@@ -1756,7 +2003,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
@@ -1780,7 +2027,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>52</v>
       </c>
@@ -1804,7 +2051,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>11</v>
@@ -1826,7 +2073,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -1850,7 +2097,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
@@ -1874,7 +2121,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
@@ -1898,7 +2145,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>14</v>
       </c>
@@ -1922,7 +2169,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>14</v>
       </c>
@@ -1946,7 +2193,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>14</v>
       </c>
@@ -1970,7 +2217,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>14</v>
       </c>
@@ -1994,7 +2241,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -2018,7 +2265,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>14</v>
       </c>
@@ -2042,7 +2289,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>14</v>
       </c>
@@ -2066,7 +2313,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
         <v>35</v>
@@ -2088,7 +2335,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>37</v>
       </c>
@@ -2112,7 +2359,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>37</v>
       </c>
@@ -2136,7 +2383,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>37</v>
       </c>
@@ -2160,7 +2407,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>37</v>
       </c>
@@ -2184,7 +2431,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>37</v>
       </c>
@@ -2208,7 +2455,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
         <v>48</v>
@@ -2230,7 +2477,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>50</v>
@@ -2252,7 +2499,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>52</v>
       </c>
@@ -2276,7 +2523,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>14</v>
       </c>
@@ -2300,7 +2547,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>14</v>
       </c>
@@ -2324,7 +2571,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>59</v>
       </c>
@@ -2348,7 +2595,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>14</v>
       </c>
@@ -2372,7 +2619,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>14</v>
       </c>
@@ -2396,7 +2643,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>52</v>
       </c>
@@ -2420,7 +2667,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>11</v>
@@ -2442,7 +2689,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>14</v>
       </c>
@@ -2466,7 +2713,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>14</v>
       </c>
@@ -2490,7 +2737,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>14</v>
       </c>
@@ -2514,7 +2761,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>14</v>
       </c>
@@ -2538,7 +2785,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>14</v>
       </c>
@@ -2562,7 +2809,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>14</v>
       </c>
@@ -2586,7 +2833,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>14</v>
       </c>
@@ -2610,7 +2857,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -2634,7 +2881,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>14</v>
       </c>
@@ -2658,7 +2905,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>14</v>
       </c>
@@ -2682,7 +2929,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>35</v>
@@ -2704,7 +2951,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>37</v>
       </c>
@@ -2728,7 +2975,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>37</v>
       </c>
@@ -2752,7 +2999,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>37</v>
       </c>
@@ -2776,7 +3023,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>37</v>
       </c>
@@ -2800,7 +3047,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>37</v>
       </c>
@@ -2824,7 +3071,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
         <v>48</v>
@@ -2846,7 +3093,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>50</v>
@@ -2868,7 +3115,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>52</v>
       </c>
@@ -2892,7 +3139,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>14</v>
       </c>
@@ -2916,7 +3163,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>14</v>
       </c>
@@ -2940,7 +3187,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>59</v>
       </c>
@@ -2964,7 +3211,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>14</v>
       </c>
@@ -2988,7 +3235,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
         <v>14</v>
       </c>
@@ -3012,7 +3259,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
         <v>52</v>
       </c>
@@ -3036,7 +3283,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A91" s="2"/>
       <c r="B91" s="2" t="s">
         <v>11</v>
@@ -3058,7 +3305,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>14</v>
       </c>
@@ -3082,7 +3329,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
         <v>14</v>
       </c>
@@ -3106,7 +3353,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
         <v>14</v>
       </c>
@@ -3130,7 +3377,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
         <v>14</v>
       </c>
@@ -3154,7 +3401,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>14</v>
       </c>
@@ -3178,7 +3425,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
         <v>14</v>
       </c>
@@ -3202,7 +3449,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
         <v>14</v>
       </c>
@@ -3226,7 +3473,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>14</v>
       </c>
@@ -3250,7 +3497,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
         <v>14</v>
       </c>
@@ -3274,7 +3521,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
         <v>14</v>
       </c>
@@ -3298,7 +3545,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A102" s="2"/>
       <c r="B102" s="2" t="s">
         <v>35</v>
@@ -3320,7 +3567,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
         <v>37</v>
       </c>
@@ -3344,7 +3591,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
         <v>37</v>
       </c>
@@ -3368,7 +3615,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
         <v>37</v>
       </c>
@@ -3392,7 +3639,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
         <v>37</v>
       </c>
@@ -3416,7 +3663,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
         <v>37</v>
       </c>
@@ -3440,7 +3687,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
         <v>48</v>
@@ -3462,7 +3709,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
         <v>50</v>
@@ -3484,7 +3731,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
         <v>52</v>
       </c>
@@ -3508,7 +3755,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
         <v>14</v>
       </c>
@@ -3532,7 +3779,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
         <v>14</v>
       </c>
@@ -3556,7 +3803,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
         <v>59</v>
       </c>
@@ -3580,7 +3827,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
         <v>14</v>
       </c>
@@ -3604,7 +3851,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
         <v>14</v>
       </c>
@@ -3628,7 +3875,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
         <v>52</v>
       </c>
@@ -3655,4 +3902,1046 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92263227-568C-46DF-958A-CFC24654ABFF}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="5" max="5" width="28.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="str">
+        <f>L3</f>
+        <v>NRG_ELC</v>
+      </c>
+      <c r="E3" t="str">
+        <f>M3&amp;" [TIMESreport "&amp;N3&amp;"]"</f>
+        <v>Electricity [TIMESreport comgroup]</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="str">
+        <f>L4</f>
+        <v>NRG_GAS</v>
+      </c>
+      <c r="E4" t="str">
+        <f>M4&amp;" [TIMESreport "&amp;N4&amp;"]"</f>
+        <v>Gas [TIMESreport comgroup]</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="str">
+        <f>L5</f>
+        <v>NRG_NUK</v>
+      </c>
+      <c r="E5" t="str">
+        <f>M5&amp;" [TIMESreport "&amp;N5&amp;"]"</f>
+        <v>Nuclear [TIMESreport comgroup]</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="str">
+        <f>L6</f>
+        <v>NRG_OIL</v>
+      </c>
+      <c r="E6" t="str">
+        <f>M6&amp;" [TIMESreport "&amp;N6&amp;"]"</f>
+        <v>Oil [TIMESreport comgroup]</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>167</v>
+      </c>
+      <c r="M6" t="s">
+        <v>127</v>
+      </c>
+      <c r="N6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="str">
+        <f>L7</f>
+        <v>NRG_RNW</v>
+      </c>
+      <c r="E7" t="str">
+        <f>M7&amp;" [TIMESreport "&amp;N7&amp;"]"</f>
+        <v>Renewable [TIMESreport comgroup]</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" t="s">
+        <v>128</v>
+      </c>
+      <c r="N7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="str">
+        <f>L8</f>
+        <v>NRG_COA</v>
+      </c>
+      <c r="E8" t="str">
+        <f>M8&amp;" [TIMESreport "&amp;N8&amp;"]"</f>
+        <v>Coal [TIMESreport comgroup]</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" t="s">
+        <v>168</v>
+      </c>
+      <c r="M8" t="s">
+        <v>169</v>
+      </c>
+      <c r="N8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F360305-D145-42E6-8DC6-C7E12995353D}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="27.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.9296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" t="str">
+        <f>L3</f>
+        <v>TR_ELE</v>
+      </c>
+      <c r="G3" t="str">
+        <f>M3&amp;" [TIMESreport "&amp;N3&amp;"]"</f>
+        <v>Electricity supply sector [TIMESreport sector]</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" ref="F4:F17" si="0">L4</f>
+        <v>TR_IND</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" ref="G4:G17" si="1">M4&amp;" [TIMESreport "&amp;N4&amp;"]"</f>
+        <v>Industry sector [TIMESreport sector]</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_MIN</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v>Mining technologies [TIMESreport sector]</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" t="s">
+        <v>132</v>
+      </c>
+      <c r="M5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_TRD</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v>Trade technologies [TIMESreport sector]</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_REF</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>Refinery  [TIMESreport sector]</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" t="s">
+        <v>134</v>
+      </c>
+      <c r="M7" t="s">
+        <v>91</v>
+      </c>
+      <c r="N7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_AGR</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>Agriculture sector [TIMESreport sector]</v>
+      </c>
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" t="s">
+        <v>135</v>
+      </c>
+      <c r="M8" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_COM</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>Commercial sector [TIMESreport sector]</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" t="s">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s">
+        <v>100</v>
+      </c>
+      <c r="N9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_RES</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v>Residential sector [TIMESreport sector]</v>
+      </c>
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" t="s">
+        <v>137</v>
+      </c>
+      <c r="M10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_TRA</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v>Transport sector [TIMESreport sector]</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" t="s">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_TRM</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v>Transmission of electricity and gas [TIMESreport sector]</v>
+      </c>
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" t="s">
+        <v>139</v>
+      </c>
+      <c r="M12" t="s">
+        <v>108</v>
+      </c>
+      <c r="N12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_PP_FOSSIL</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fossile power plants [TIMESreport techgroup]</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+      <c r="L13" t="s">
+        <v>159</v>
+      </c>
+      <c r="M13" t="s">
+        <v>140</v>
+      </c>
+      <c r="N13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_PP_NUCLEAR</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="1"/>
+        <v>Nuclear power plants [TIMESreport techgroup]</v>
+      </c>
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" t="s">
+        <v>160</v>
+      </c>
+      <c r="M14" t="s">
+        <v>141</v>
+      </c>
+      <c r="N14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_PP_RENEW</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="1"/>
+        <v>Renewable power plant [TIMESreport techgroup]</v>
+      </c>
+      <c r="H15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" t="s">
+        <v>161</v>
+      </c>
+      <c r="M15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_ES_STEEL</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="1"/>
+        <v>Steel service [TIMESreport service]</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" t="s">
+        <v>145</v>
+      </c>
+      <c r="N16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>TR_ES_OTH</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="1"/>
+        <v>Other [TIMESreport service]</v>
+      </c>
+      <c r="H17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" t="s">
+        <v>152</v>
+      </c>
+      <c r="M17" t="s">
+        <v>149</v>
+      </c>
+      <c r="N17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" ref="F18:F20" si="2">L18</f>
+        <v>TR_ES_SP</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" ref="G18:G20" si="3">M18&amp;" [TIMESreport "&amp;N18&amp;"]"</f>
+        <v>Space heating [TIMESreport service]</v>
+      </c>
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" t="s">
+        <v>154</v>
+      </c>
+      <c r="M18" t="s">
+        <v>147</v>
+      </c>
+      <c r="N18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="2"/>
+        <v>TR_ES_APP</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="3"/>
+        <v>Appliances [TIMESreport service]</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M19" t="s">
+        <v>148</v>
+      </c>
+      <c r="N19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="2"/>
+        <v>TR_ES_TR</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="3"/>
+        <v>Transport [TIMESreport service]</v>
+      </c>
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" t="s">
+        <v>176</v>
+      </c>
+      <c r="M20" t="s">
+        <v>177</v>
+      </c>
+      <c r="N20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" ref="F21:F22" si="4">L21</f>
+        <v>TR_STEEL</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" ref="G21:G22" si="5">M21&amp;" [TIMESreport "&amp;N21&amp;"]"</f>
+        <v>Iron&amp;Stell [TIMESreport subsector]</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+      <c r="L21" t="s">
+        <v>158</v>
+      </c>
+      <c r="M21" t="s">
+        <v>156</v>
+      </c>
+      <c r="N21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="4"/>
+        <v>TR_TRAPUB</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="5"/>
+        <v>Public Transport [TIMESreport subsector]</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22" t="s">
+        <v>170</v>
+      </c>
+      <c r="M22" t="s">
+        <v>171</v>
+      </c>
+      <c r="N22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" ref="F23" si="6">L23</f>
+        <v>TR_TRACAR</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" ref="G23" si="7">M23&amp;" [TIMESreport "&amp;N23&amp;"]"</f>
+        <v>Car transport [TIMESreport subsector]</v>
+      </c>
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" t="s">
+        <v>175</v>
+      </c>
+      <c r="M23" t="s">
+        <v>174</v>
+      </c>
+      <c r="N23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>157</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" ref="F24:F27" si="8">L24</f>
+        <v>Mt-y</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" ref="G24:G26" si="9">M24&amp;" [TIMESreport "&amp;N24&amp;"]"</f>
+        <v>Million ton a year [TIMESreport capacityunit]</v>
+      </c>
+      <c r="H24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24" t="s">
+        <v>163</v>
+      </c>
+      <c r="N24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="8"/>
+        <v>PJa</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="9"/>
+        <v>PJ annually [TIMESreport capacityunit]</v>
+      </c>
+      <c r="H25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" t="s">
+        <v>180</v>
+      </c>
+      <c r="M25" t="s">
+        <v>181</v>
+      </c>
+      <c r="N25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="8"/>
+        <v>GW</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="9"/>
+        <v>GW [TIMESreport capacityunit]</v>
+      </c>
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" t="s">
+        <v>182</v>
+      </c>
+      <c r="M26" t="s">
+        <v>182</v>
+      </c>
+      <c r="N26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="8"/>
+        <v>000_Units</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" ref="G27" si="10">M27&amp;" [TIMESreport "&amp;N27&amp;"]"</f>
+        <v>1000 units [TIMESreport capacityunit]</v>
+      </c>
+      <c r="H27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" t="s">
+        <v>185</v>
+      </c>
+      <c r="M27" t="s">
+        <v>186</v>
+      </c>
+      <c r="N27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sets-DemoModels.xlsx
+++ b/Sets-DemoModels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kristoffer\DemoS_012_timesreport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\Demo_models\DemoS_012_timesreport-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E15EBF-3D8E-43F6-B664-4A91876615C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6341B32A-B8C4-44F1-AD21-F37528D9EA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="2" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
+    <workbookView xWindow="25060" yWindow="0" windowWidth="13310" windowHeight="21000" activeTab="2" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="188">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -600,6 +600,9 @@
   </si>
   <si>
     <t>1000 units</t>
+  </si>
+  <si>
+    <t>*ELC</t>
   </si>
 </sst>
 </file>
@@ -998,23 +1001,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD03DB1-DD55-4548-B86E-1F92E13CF8ED}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="65.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="56" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1040,7 +1043,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>72</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1071,7 +1074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -1102,7 +1105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>79</v>
       </c>
@@ -1116,7 +1119,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>81</v>
       </c>
@@ -1130,7 +1133,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>83</v>
       </c>
@@ -1152,18 +1155,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06336B7-5D6A-48EE-B122-F085391548AD}">
   <dimension ref="A1:J116"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>115</v>
@@ -1219,7 +1222,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>110</v>
@@ -1243,7 +1246,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>53</v>
@@ -1267,7 +1270,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -1291,7 +1294,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>90</v>
@@ -1315,7 +1318,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>93</v>
@@ -1339,7 +1342,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>96</v>
@@ -1363,7 +1366,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>111</v>
@@ -1387,7 +1390,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>106</v>
@@ -1411,7 +1414,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>109</v>
@@ -1435,7 +1438,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>11</v>
@@ -1457,7 +1460,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1481,7 +1484,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1505,7 +1508,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1529,7 +1532,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -1553,7 +1556,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1577,7 +1580,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
@@ -1601,7 +1604,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
@@ -1625,7 +1628,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
@@ -1649,7 +1652,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
@@ -1673,7 +1676,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
@@ -1697,7 +1700,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>35</v>
@@ -1719,7 +1722,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>37</v>
       </c>
@@ -1767,7 +1770,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
@@ -1791,7 +1794,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -1815,7 +1818,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
@@ -1839,7 +1842,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>48</v>
@@ -1861,7 +1864,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>50</v>
@@ -1883,7 +1886,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>52</v>
       </c>
@@ -1907,7 +1910,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
@@ -1931,7 +1934,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
@@ -1955,7 +1958,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>59</v>
       </c>
@@ -1979,7 +1982,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
@@ -2003,7 +2006,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
@@ -2027,7 +2030,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>52</v>
       </c>
@@ -2051,7 +2054,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>11</v>
@@ -2073,7 +2076,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -2097,7 +2100,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
@@ -2121,7 +2124,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
@@ -2145,7 +2148,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>14</v>
       </c>
@@ -2169,7 +2172,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>14</v>
       </c>
@@ -2193,7 +2196,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>14</v>
       </c>
@@ -2217,7 +2220,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>14</v>
       </c>
@@ -2241,7 +2244,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
@@ -2265,7 +2268,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>14</v>
       </c>
@@ -2289,7 +2292,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>14</v>
       </c>
@@ -2313,7 +2316,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
         <v>35</v>
@@ -2335,7 +2338,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>37</v>
       </c>
@@ -2359,7 +2362,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>37</v>
       </c>
@@ -2383,7 +2386,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>37</v>
       </c>
@@ -2407,7 +2410,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>37</v>
       </c>
@@ -2431,7 +2434,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>37</v>
       </c>
@@ -2455,7 +2458,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
         <v>48</v>
@@ -2477,7 +2480,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>50</v>
@@ -2499,7 +2502,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>52</v>
       </c>
@@ -2523,7 +2526,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>14</v>
       </c>
@@ -2547,7 +2550,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>14</v>
       </c>
@@ -2571,7 +2574,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>59</v>
       </c>
@@ -2595,7 +2598,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>14</v>
       </c>
@@ -2619,7 +2622,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>14</v>
       </c>
@@ -2643,7 +2646,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>52</v>
       </c>
@@ -2667,7 +2670,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>11</v>
@@ -2689,7 +2692,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>14</v>
       </c>
@@ -2713,7 +2716,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>14</v>
       </c>
@@ -2737,7 +2740,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>14</v>
       </c>
@@ -2761,7 +2764,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>14</v>
       </c>
@@ -2785,7 +2788,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>14</v>
       </c>
@@ -2809,7 +2812,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>14</v>
       </c>
@@ -2833,7 +2836,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>14</v>
       </c>
@@ -2857,7 +2860,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -2881,7 +2884,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>14</v>
       </c>
@@ -2905,7 +2908,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>14</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>35</v>
@@ -2951,7 +2954,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>37</v>
       </c>
@@ -2975,7 +2978,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>37</v>
       </c>
@@ -2999,7 +3002,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>37</v>
       </c>
@@ -3023,7 +3026,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>37</v>
       </c>
@@ -3047,7 +3050,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>37</v>
       </c>
@@ -3071,7 +3074,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
         <v>48</v>
@@ -3093,7 +3096,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>50</v>
@@ -3115,7 +3118,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>52</v>
       </c>
@@ -3139,7 +3142,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>14</v>
       </c>
@@ -3163,7 +3166,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>14</v>
       </c>
@@ -3187,7 +3190,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>59</v>
       </c>
@@ -3211,7 +3214,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>14</v>
       </c>
@@ -3235,7 +3238,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>14</v>
       </c>
@@ -3259,7 +3262,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>52</v>
       </c>
@@ -3283,7 +3286,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
       <c r="B91" s="2" t="s">
         <v>11</v>
@@ -3305,7 +3308,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>14</v>
       </c>
@@ -3329,7 +3332,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>14</v>
       </c>
@@ -3353,7 +3356,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>14</v>
       </c>
@@ -3377,7 +3380,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>14</v>
       </c>
@@ -3401,7 +3404,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>14</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>14</v>
       </c>
@@ -3449,7 +3452,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>14</v>
       </c>
@@ -3473,7 +3476,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>14</v>
       </c>
@@ -3497,7 +3500,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>14</v>
       </c>
@@ -3521,7 +3524,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>14</v>
       </c>
@@ -3545,7 +3548,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
       <c r="B102" s="2" t="s">
         <v>35</v>
@@ -3567,7 +3570,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>37</v>
       </c>
@@ -3591,7 +3594,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>37</v>
       </c>
@@ -3615,7 +3618,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>37</v>
       </c>
@@ -3639,7 +3642,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>37</v>
       </c>
@@ -3663,7 +3666,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>37</v>
       </c>
@@ -3687,7 +3690,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
         <v>48</v>
@@ -3709,7 +3712,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
         <v>50</v>
@@ -3731,7 +3734,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>52</v>
       </c>
@@ -3755,7 +3758,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>14</v>
       </c>
@@ -3779,7 +3782,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>14</v>
       </c>
@@ -3803,7 +3806,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>59</v>
       </c>
@@ -3827,7 +3830,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>14</v>
       </c>
@@ -3851,7 +3854,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>14</v>
       </c>
@@ -3875,7 +3878,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>52</v>
       </c>
@@ -3910,17 +3913,17 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>69</v>
       </c>
@@ -3955,19 +3958,19 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="D3" t="str">
-        <f>L3</f>
+        <f t="shared" ref="D3:D8" si="0">L3</f>
         <v>NRG_ELC</v>
       </c>
       <c r="E3" t="str">
-        <f>M3&amp;" [TIMESreport "&amp;N3&amp;"]"</f>
+        <f t="shared" ref="E3:E8" si="1">M3&amp;" [TIMESreport "&amp;N3&amp;"]"</f>
         <v>Electricity [TIMESreport comgroup]</v>
       </c>
       <c r="F3" t="s">
@@ -3986,7 +3989,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>166</v>
       </c>
@@ -3994,11 +3997,11 @@
         <v>21</v>
       </c>
       <c r="D4" t="str">
-        <f>L4</f>
+        <f t="shared" si="0"/>
         <v>NRG_GAS</v>
       </c>
       <c r="E4" t="str">
-        <f>M4&amp;" [TIMESreport "&amp;N4&amp;"]"</f>
+        <f t="shared" si="1"/>
         <v>Gas [TIMESreport comgroup]</v>
       </c>
       <c r="F4" t="s">
@@ -4017,7 +4020,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>166</v>
       </c>
@@ -4025,11 +4028,11 @@
         <v>25</v>
       </c>
       <c r="D5" t="str">
-        <f>L5</f>
+        <f t="shared" si="0"/>
         <v>NRG_NUK</v>
       </c>
       <c r="E5" t="str">
-        <f>M5&amp;" [TIMESreport "&amp;N5&amp;"]"</f>
+        <f t="shared" si="1"/>
         <v>Nuclear [TIMESreport comgroup]</v>
       </c>
       <c r="F5" t="s">
@@ -4048,7 +4051,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>166</v>
       </c>
@@ -4056,11 +4059,11 @@
         <v>79</v>
       </c>
       <c r="D6" t="str">
-        <f>L6</f>
+        <f t="shared" si="0"/>
         <v>NRG_OIL</v>
       </c>
       <c r="E6" t="str">
-        <f>M6&amp;" [TIMESreport "&amp;N6&amp;"]"</f>
+        <f t="shared" si="1"/>
         <v>Oil [TIMESreport comgroup]</v>
       </c>
       <c r="F6" t="s">
@@ -4079,7 +4082,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>166</v>
       </c>
@@ -4087,11 +4090,11 @@
         <v>81</v>
       </c>
       <c r="D7" t="str">
-        <f>L7</f>
+        <f t="shared" si="0"/>
         <v>NRG_RNW</v>
       </c>
       <c r="E7" t="str">
-        <f>M7&amp;" [TIMESreport "&amp;N7&amp;"]"</f>
+        <f t="shared" si="1"/>
         <v>Renewable [TIMESreport comgroup]</v>
       </c>
       <c r="F7" t="s">
@@ -4110,7 +4113,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>166</v>
       </c>
@@ -4118,11 +4121,11 @@
         <v>19</v>
       </c>
       <c r="D8" t="str">
-        <f>L8</f>
+        <f t="shared" si="0"/>
         <v>NRG_COA</v>
       </c>
       <c r="E8" t="str">
-        <f>M8&amp;" [TIMESreport "&amp;N8&amp;"]"</f>
+        <f t="shared" si="1"/>
         <v>Coal [TIMESreport comgroup]</v>
       </c>
       <c r="F8" t="s">
@@ -4152,22 +4155,22 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.9296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4208,7 +4211,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>115</v>
       </c>
@@ -4236,7 +4239,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>110</v>
       </c>
@@ -4264,7 +4267,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>53</v>
       </c>
@@ -4292,7 +4295,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>165</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>90</v>
       </c>
@@ -4348,7 +4351,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>93</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>96</v>
       </c>
@@ -4404,7 +4407,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>111</v>
       </c>
@@ -4432,7 +4435,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>106</v>
       </c>
@@ -4460,7 +4463,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>109</v>
       </c>
@@ -4488,7 +4491,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -4519,7 +4522,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -4550,7 +4553,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4581,7 +4584,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>143</v>
       </c>
@@ -4612,7 +4615,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>143</v>
       </c>
@@ -4643,7 +4646,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>143</v>
       </c>
@@ -4674,7 +4677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>143</v>
       </c>
@@ -4705,7 +4708,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>143</v>
       </c>
@@ -4736,7 +4739,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>157</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -4795,7 +4798,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>143</v>
       </c>
@@ -4826,7 +4829,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>157</v>
       </c>
@@ -4854,7 +4857,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>184</v>
       </c>
@@ -4885,7 +4888,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>130</v>
       </c>
@@ -4913,7 +4916,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>138</v>
       </c>

--- a/Sets-DemoModels.xlsx
+++ b/Sets-DemoModels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\Demo_models\DemoS_012_timesreport-master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kristoffer\DemoS_012_timesreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6341B32A-B8C4-44F1-AD21-F37528D9EA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7684F212-534F-45FA-80FD-869BDB4EC69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25060" yWindow="0" windowWidth="13310" windowHeight="21000" activeTab="2" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
+    <workbookView xWindow="4440" yWindow="2970" windowWidth="25395" windowHeight="9195" activeTab="3" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="TIMESreport_Sets-Comm" sheetId="3" r:id="rId3"/>
     <sheet name="TIMESreport_Sets-Proc" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TIMESreport_Sets-Proc'!$A$2:$N$54</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,8 +41,274 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Kristoffer Steen Andersen</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{942B26F1-E7E3-4CB4-BF4E-1633C8218078}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Column A:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> Name of TIMESreport commodity set
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Column B:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> Description of TIMESreport commodity set (used to define labels downstream)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Column C: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Specifies which TIMESreport dimension the commodity set belongs to
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Columns E-K:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> Standard VEDA filtering approach for each TIMESreport commodity set
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Note:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> When defining sets for a specific TIMESreport dimension, ensure that each commodity belongs to only one element within that dimension. For example, a commodity cannot be part of both NRG_ELC (Electricity) and NRG_GAS (Gas), as this would result in double-counting. If such overlap occurs, timesreport.gms will abort execution.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User flexibility</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>: The naming conventions, set definitions, and dimension structure are fully customizable by the user. However, modifying the dimensions, e.g., adding additional commodity dimensions to timesreport, requires GAMS programming skills, as changes must be reflected in the timesreport.gms code.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Kristoffer Steen Andersen</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{5FE19655-0160-4772-9D1D-F36D7641D2AF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Column A</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: Name of TIMESreport process set
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Column B</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: Description of TIMESreport process set (used to define labels downstream)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Column C</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: Specifies which TIMESreport dimension the process set belongs to
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Columns E-M</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: Standard VEDA filtering approach for each TIMESreport process set
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Note:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> When defining sets for a specific TIMESreport dimension, ensure that each process belongs to only one element within that dimension. For example, a process cannot be part of both SC_AGR (Agriculture sector) and SC_COM (Commercial Sector), as this would result in double-counting. If such overlap occurs, timesreport.gms will abort execution.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User flexibility</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>: The naming conventions, set definitions, and dimension structure are fully customizable by the user. However, modifying or adding to additional dimensions (capacityunit, sector, service, subsector, techgroup) requires GAMS programming skills, as changes must be reflected in the timesreport.gms code.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="276">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -431,105 +700,18 @@
     <t>TFM_Csets</t>
   </si>
   <si>
-    <t>TR_ELE</t>
-  </si>
-  <si>
-    <t>TR_IND</t>
-  </si>
-  <si>
-    <t>TR_MIN</t>
-  </si>
-  <si>
-    <t>TR_TRD</t>
-  </si>
-  <si>
-    <t>TR_REF</t>
-  </si>
-  <si>
-    <t>TR_AGR</t>
-  </si>
-  <si>
-    <t>TR_COM</t>
-  </si>
-  <si>
-    <t>TR_RES</t>
-  </si>
-  <si>
-    <t>TR_TRA</t>
-  </si>
-  <si>
-    <t>TR_TRM</t>
-  </si>
-  <si>
-    <t>Fossile power plants</t>
-  </si>
-  <si>
-    <t>Nuclear power plants</t>
-  </si>
-  <si>
-    <t>Renewable power plant</t>
-  </si>
-  <si>
     <t>DMD</t>
   </si>
   <si>
     <t>DIIS</t>
   </si>
   <si>
-    <t>Steel service</t>
-  </si>
-  <si>
-    <t>TR_ES_STEEL</t>
-  </si>
-  <si>
-    <t>Space heating</t>
-  </si>
-  <si>
     <t>Appliances</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>DRSH,DCSH</t>
-  </si>
-  <si>
-    <t>DRAP,DCAP</t>
-  </si>
-  <si>
-    <t>TR_ES_OTH</t>
-  </si>
-  <si>
-    <t>TR_ES_APP</t>
-  </si>
-  <si>
-    <t>TR_ES_SP</t>
-  </si>
-  <si>
-    <t>DIDM1,DROT,DCOT,DAOT</t>
-  </si>
-  <si>
-    <t>Iron&amp;Stell</t>
-  </si>
-  <si>
     <t>ITIISIN,ITIISIBF,ITIISBOF,IDMIIS</t>
   </si>
   <si>
-    <t>TR_STEEL</t>
-  </si>
-  <si>
-    <t>TR_PP_FOSSIL</t>
-  </si>
-  <si>
-    <t>TR_PP_NUCLEAR</t>
-  </si>
-  <si>
-    <t>TR_PP_RENEW</t>
-  </si>
-  <si>
-    <t>Mt-y</t>
-  </si>
-  <si>
     <t>Million ton a year</t>
   </si>
   <si>
@@ -551,33 +733,6 @@
     <t>Coal</t>
   </si>
   <si>
-    <t>TR_TRAPUB</t>
-  </si>
-  <si>
-    <t>Public Transport</t>
-  </si>
-  <si>
-    <t>TCAR*</t>
-  </si>
-  <si>
-    <t>TPUB*</t>
-  </si>
-  <si>
-    <t>Car transport</t>
-  </si>
-  <si>
-    <t>TR_TRACAR</t>
-  </si>
-  <si>
-    <t>TR_ES_TR</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>DTCAR,DTPUB</t>
-  </si>
-  <si>
     <t>capacityunit</t>
   </si>
   <si>
@@ -603,16 +758,396 @@
   </si>
   <si>
     <t>*ELC</t>
+  </si>
+  <si>
+    <t>SS_ELE</t>
+  </si>
+  <si>
+    <t>Power plants</t>
+  </si>
+  <si>
+    <t>SS_CHP</t>
+  </si>
+  <si>
+    <t>Combined heat and power plant</t>
+  </si>
+  <si>
+    <t>SS_HPL</t>
+  </si>
+  <si>
+    <t>Heating plant</t>
+  </si>
+  <si>
+    <t>CHP</t>
+  </si>
+  <si>
+    <t>HPL</t>
+  </si>
+  <si>
+    <t>IISRST</t>
+  </si>
+  <si>
+    <t>Industrial Steel</t>
+  </si>
+  <si>
+    <t>IISIRO</t>
+  </si>
+  <si>
+    <t>Industrial Iron</t>
+  </si>
+  <si>
+    <t>Industrial Ore</t>
+  </si>
+  <si>
+    <t>Industrial Sinter</t>
+  </si>
+  <si>
+    <t>SS_IRO</t>
+  </si>
+  <si>
+    <t>SS_STE</t>
+  </si>
+  <si>
+    <t>SS_ORE</t>
+  </si>
+  <si>
+    <t>SS_SIN</t>
+  </si>
+  <si>
+    <t>IISSIN</t>
+  </si>
+  <si>
+    <t>Industrial IronSteel Demand</t>
+  </si>
+  <si>
+    <t>SS_OIL</t>
+  </si>
+  <si>
+    <t>SS_COA</t>
+  </si>
+  <si>
+    <t>SS_GAS</t>
+  </si>
+  <si>
+    <t>SS_REW</t>
+  </si>
+  <si>
+    <t>MINSOL*,MINWIN*,MINHYD*</t>
+  </si>
+  <si>
+    <t>SS_BIO</t>
+  </si>
+  <si>
+    <t>MINBIO*</t>
+  </si>
+  <si>
+    <t>SS_OXY</t>
+  </si>
+  <si>
+    <t>MININDOXY</t>
+  </si>
+  <si>
+    <t>SS_NUC</t>
+  </si>
+  <si>
+    <t>MINNUC*</t>
+  </si>
+  <si>
+    <t>MINCOA*,IMPCOA*,EXPCOA*</t>
+  </si>
+  <si>
+    <t>MINGAS*,IMPGAS*,EXPGAS*</t>
+  </si>
+  <si>
+    <t>MINOIL*,IMPOIL*,IMPHFO*,IMPGSL*,IMPDSL*,IMPKER*,IMPLPG*,IMPNAP*, IMPPOP*,EXPOIL*,EXPHFO*,EXPGSL*,EXPDSL*,EXPKER*,EXPLPG*,EXPNAP*, EXPPOP*</t>
+  </si>
+  <si>
+    <t>SS_ELC</t>
+  </si>
+  <si>
+    <t>Electricity trade</t>
+  </si>
+  <si>
+    <t>IMPELC*,EXPELC*</t>
+  </si>
+  <si>
+    <t>SS_REF</t>
+  </si>
+  <si>
+    <t>Oil refinary</t>
+  </si>
+  <si>
+    <t>REFEOIL00</t>
+  </si>
+  <si>
+    <t>SS_AGR</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>AOTETOT</t>
+  </si>
+  <si>
+    <t>SS_COM</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Other demands</t>
+  </si>
+  <si>
+    <t>Room heat</t>
+  </si>
+  <si>
+    <t>Agricultural demand</t>
+  </si>
+  <si>
+    <t>CA*,RA*</t>
+  </si>
+  <si>
+    <t>CO*,RO*</t>
+  </si>
+  <si>
+    <t>CS*,RS*</t>
+  </si>
+  <si>
+    <t>SS_RES</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>SS_TRC</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>SS_TRP</t>
+  </si>
+  <si>
+    <t>Public transport</t>
+  </si>
+  <si>
+    <t>Private transport</t>
+  </si>
+  <si>
+    <t>SS_TRMG</t>
+  </si>
+  <si>
+    <t>SS_TRME</t>
+  </si>
+  <si>
+    <t>Gas transmission</t>
+  </si>
+  <si>
+    <t>Electricity transmission</t>
+  </si>
+  <si>
+    <t>TB_ELC*</t>
+  </si>
+  <si>
+    <t>TU_GAS*</t>
+  </si>
+  <si>
+    <t>Oil supply</t>
+  </si>
+  <si>
+    <t>Coal supply</t>
+  </si>
+  <si>
+    <t>Natural gas supply</t>
+  </si>
+  <si>
+    <t>Renewable energy supply</t>
+  </si>
+  <si>
+    <t>Domestic biomass supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxygen supply </t>
+  </si>
+  <si>
+    <t>Mining nuclear fuel supply</t>
+  </si>
+  <si>
+    <t>TP*</t>
+  </si>
+  <si>
+    <t>TC*</t>
+  </si>
+  <si>
+    <t>TG_OIL</t>
+  </si>
+  <si>
+    <t>TG_BIO</t>
+  </si>
+  <si>
+    <t>TG_NUC</t>
+  </si>
+  <si>
+    <t>TG_REW</t>
+  </si>
+  <si>
+    <t>TG_ELC</t>
+  </si>
+  <si>
+    <t>TG_GAS</t>
+  </si>
+  <si>
+    <t>*BIO*,</t>
+  </si>
+  <si>
+    <t>*NUC*,</t>
+  </si>
+  <si>
+    <t>*SOL*,*WIN*,*HYD*</t>
+  </si>
+  <si>
+    <t>*OIL*,*HFO*,*GSL*,*DSL*,*KER*,*LPG*,*NAP*,*POP*</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>SC_TRM</t>
+  </si>
+  <si>
+    <t>SC_TRD</t>
+  </si>
+  <si>
+    <t>SC_TRA</t>
+  </si>
+  <si>
+    <t>SC_RES</t>
+  </si>
+  <si>
+    <t>SC_REF</t>
+  </si>
+  <si>
+    <t>SC_MIN</t>
+  </si>
+  <si>
+    <t>SC_IND</t>
+  </si>
+  <si>
+    <t>SC_ELE</t>
+  </si>
+  <si>
+    <t>SC_COM</t>
+  </si>
+  <si>
+    <t>SC_AGR</t>
+  </si>
+  <si>
+    <t>SR_AGR</t>
+  </si>
+  <si>
+    <t>SR_APP</t>
+  </si>
+  <si>
+    <t>SR_OTH</t>
+  </si>
+  <si>
+    <t>SR_RHT</t>
+  </si>
+  <si>
+    <t>SR_TRC</t>
+  </si>
+  <si>
+    <t>SR_TRP</t>
+  </si>
+  <si>
+    <t>TG_COA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coal </t>
+  </si>
+  <si>
+    <t>NRG_BIO</t>
+  </si>
+  <si>
+    <t>R*,-REFEOIL00</t>
+  </si>
+  <si>
+    <t>Mta</t>
+  </si>
+  <si>
+    <t>SR_IRS</t>
+  </si>
+  <si>
+    <t>IISORE,MINIISORE</t>
+  </si>
+  <si>
+    <t>*SOL*,*WIN*,*RNW*,*HYD*,-*SOLID*,-ELCRNW,-RNW</t>
+  </si>
+  <si>
+    <t>*BIO*,*BIO</t>
+  </si>
+  <si>
+    <t>ENV_CO2</t>
+  </si>
+  <si>
+    <t>ENV</t>
+  </si>
+  <si>
+    <t>*CO2</t>
+  </si>
+  <si>
+    <t>IDM1ETOT</t>
+  </si>
+  <si>
+    <t>SS_IND</t>
+  </si>
+  <si>
+    <t>Industry other</t>
+  </si>
+  <si>
+    <t>SR_IND</t>
+  </si>
+  <si>
+    <t>TG_DMD</t>
+  </si>
+  <si>
+    <t>Demand Technology</t>
+  </si>
+  <si>
+    <t>AOTETOT, IDM1ETOT</t>
+  </si>
+  <si>
+    <t>DEM_COM</t>
+  </si>
+  <si>
+    <t>Demand commodity</t>
+  </si>
+  <si>
+    <t>DEM</t>
+  </si>
+  <si>
+    <t>GHG-emission</t>
+  </si>
+  <si>
+    <t>IDMIIS</t>
+  </si>
+  <si>
+    <t>DCOT,DCSH,DAOT,DCAP,DIDM1,DRAP,DROT,DRSH,DTCAR,DTPUB,DIIS</t>
+  </si>
+  <si>
+    <t>Industry Demand</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="165" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,8 +1170,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -655,8 +1234,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -665,30 +1256,124 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" applyBorder="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="23"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="31">
+    <cellStyle name="5x indented GHG Textfiels" xfId="2" xr:uid="{0FB2083B-5C34-47A0-BE95-276FE0B9770C}"/>
+    <cellStyle name="AggOrange_CRFReport-template" xfId="3" xr:uid="{164EDF9C-1345-4285-A590-72E92C418028}"/>
+    <cellStyle name="AggOrange9_CRFReport-template" xfId="4" xr:uid="{7A2E8B0B-A172-405E-B655-610DAC318C60}"/>
+    <cellStyle name="CustomizationCells" xfId="5" xr:uid="{2B02F197-BB62-4282-A0FB-67B255CB7871}"/>
+    <cellStyle name="Euro" xfId="6" xr:uid="{5ABD2E6B-4F5B-4FE2-9054-9798B0268F88}"/>
+    <cellStyle name="InputCells" xfId="7" xr:uid="{59D2DDF5-E990-4D73-8279-FF490C763849}"/>
+    <cellStyle name="Migliaia_tab emissioni" xfId="21" xr:uid="{C9AFF767-3C09-4056-A5C6-5EFD71374C05}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="8" xr:uid="{B22C9995-6E64-4E7A-9C93-5C8C36FC0748}"/>
+    <cellStyle name="Normal 10 2" xfId="19" xr:uid="{3A68CEB6-B267-43CD-A80A-69D8322BAE37}"/>
+    <cellStyle name="Normal 11" xfId="28" xr:uid="{F97EA0D5-487D-4116-9607-3BEB1CA32B6E}"/>
+    <cellStyle name="Normal 12" xfId="23" xr:uid="{8D2A0BBA-0528-4397-900B-6D96E199F205}"/>
+    <cellStyle name="Normal 2" xfId="9" xr:uid="{62134BF4-8887-4886-9159-C353664C4E93}"/>
+    <cellStyle name="Normal 3" xfId="10" xr:uid="{5AA0F7C3-3582-4C87-B283-9B7D69484195}"/>
+    <cellStyle name="Normal 3 2" xfId="27" xr:uid="{6FFD48F4-2248-436D-BAC1-2BF3AFDD0324}"/>
+    <cellStyle name="Normal 3 3" xfId="30" xr:uid="{AAB53E4D-39CB-4C21-A670-E7A674143D64}"/>
+    <cellStyle name="Normal 4" xfId="11" xr:uid="{9B67B6A7-5EA3-456B-A559-EA7CFC7CA5CF}"/>
     <cellStyle name="Normal 5" xfId="1" xr:uid="{B387DD4F-F719-4379-A4FC-680701E911D2}"/>
+    <cellStyle name="Normal 5 2" xfId="26" xr:uid="{EC443464-2DF2-477D-919C-92F1557FA9FE}"/>
+    <cellStyle name="Normal 5 3" xfId="29" xr:uid="{2264DF01-97E2-4FE1-9793-C831AF5424A3}"/>
+    <cellStyle name="Normal 6" xfId="20" xr:uid="{766BC6C5-346A-4CAC-91AF-BBFE8FFB071A}"/>
+    <cellStyle name="Normal 7" xfId="22" xr:uid="{88CD0106-675A-4B14-8A3E-2F4148FD9714}"/>
+    <cellStyle name="Normal 8" xfId="24" xr:uid="{60A7F545-E99D-47AE-A99D-604B7A192563}"/>
+    <cellStyle name="Normal 9" xfId="25" xr:uid="{53D6706E-923C-4BB5-AE55-716FD874A845}"/>
+    <cellStyle name="Normal GHG Numbers (0.00)" xfId="12" xr:uid="{7D199897-9DCA-41DD-A62F-5B1B459715F7}"/>
+    <cellStyle name="Normal GHG Textfiels Bold" xfId="13" xr:uid="{517FA2F6-00A8-4B2F-93B3-CB1F2E12BB06}"/>
+    <cellStyle name="Normal GHG-Shade" xfId="14" xr:uid="{20EC4AB8-9C1E-4B72-8CA6-6F9027FB5200}"/>
+    <cellStyle name="Normale_B2020" xfId="15" xr:uid="{F175AF03-F959-40DB-AB54-7CD7D2C0050D}"/>
+    <cellStyle name="Percent 2" xfId="16" xr:uid="{4BB3658D-C2B8-47C8-A102-E0EF5481323E}"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="17" xr:uid="{99EEC642-FF20-4538-9E84-4B4FC758D80D}"/>
+    <cellStyle name="Обычный_CRF2002 (1)" xfId="18" xr:uid="{0AD22835-B9E3-4CD8-BFAD-DA6B7F27324E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1163,7 +1848,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -3908,1043 +4593,1979 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92263227-568C-46DF-958A-CFC24654ABFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92263227-568C-46DF-958A-CFC24654ABFF}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" t="str">
-        <f t="shared" ref="D3:D8" si="0">L3</f>
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E11" si="0">A3</f>
         <v>NRG_ELC</v>
       </c>
-      <c r="E3" t="str">
-        <f t="shared" ref="E3:E8" si="1">M3&amp;" [TIMESreport "&amp;N3&amp;"]"</f>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F11" si="1">B3&amp;" [TIMESreport "&amp;C3&amp;"]"</f>
         <v>Electricity [TIMESreport comgroup]</v>
       </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" t="s">
-        <v>124</v>
-      </c>
-      <c r="N3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <f t="shared" si="0"/>
         <v>NRG_GAS</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <f t="shared" si="1"/>
         <v>Gas [TIMESreport comgroup]</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
       <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M4" t="s">
-        <v>125</v>
-      </c>
-      <c r="N4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <f t="shared" si="0"/>
         <v>NRG_NUK</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <f t="shared" si="1"/>
         <v>Nuclear [TIMESreport comgroup]</v>
       </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
       <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" t="s">
-        <v>126</v>
-      </c>
-      <c r="N5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <f t="shared" si="0"/>
         <v>NRG_OIL</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <f t="shared" si="1"/>
         <v>Oil [TIMESreport comgroup]</v>
       </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
       <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" t="s">
-        <v>167</v>
-      </c>
-      <c r="M6" t="s">
-        <v>127</v>
-      </c>
-      <c r="N6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <f t="shared" si="0"/>
         <v>NRG_RNW</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <f t="shared" si="1"/>
         <v>Renewable [TIMESreport comgroup]</v>
       </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
       <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M7" t="s">
-        <v>128</v>
-      </c>
-      <c r="N7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H7" t="s">
+        <v>257</v>
+      </c>
+      <c r="J7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="str">
+      <c r="E8" t="str">
         <f t="shared" si="0"/>
         <v>NRG_COA</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <f t="shared" si="1"/>
         <v>Coal [TIMESreport comgroup]</v>
       </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
       <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L8" t="s">
-        <v>168</v>
-      </c>
-      <c r="M8" t="s">
-        <v>169</v>
-      </c>
-      <c r="N8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" t="s">
         <v>123</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>NRG_BIO</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>Biomass [TIMESreport comgroup]</v>
+      </c>
+      <c r="G9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" t="s">
+        <v>258</v>
+      </c>
+      <c r="J9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>ENV_CO2</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>GHG-emission [TIMESreport comgroup]</v>
+      </c>
+      <c r="G10" t="s">
+        <v>260</v>
+      </c>
+      <c r="H10" t="s">
+        <v>261</v>
+      </c>
+      <c r="J10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v>DEM_COM</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v>Demand commodity [TIMESreport comgroup]</v>
+      </c>
+      <c r="G11" t="s">
+        <v>271</v>
+      </c>
+      <c r="H11" t="s">
+        <v>274</v>
+      </c>
+      <c r="J11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F360305-D145-42E6-8DC6-C7E12995353D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F360305-D145-42E6-8DC6-C7E12995353D}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="143.26953125" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>147</v>
+      </c>
       <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E36" si="0">A3</f>
+        <v>000_Units</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F36" si="1">B3&amp;" [TIMESreport "&amp;C3&amp;"]"</f>
+        <v>1000 units [TIMESreport capacityunit]</v>
+      </c>
+      <c r="H3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v>GW</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v>GW [TIMESreport capacityunit]</v>
+      </c>
+      <c r="H4" t="s">
         <v>115</v>
       </c>
-      <c r="F3" t="str">
-        <f>L3</f>
-        <v>TR_ELE</v>
-      </c>
-      <c r="G3" t="str">
-        <f>M3&amp;" [TIMESreport "&amp;N3&amp;"]"</f>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" t="str">
+        <f>A5</f>
+        <v>Mta</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>Million ton a year [TIMESreport capacityunit]</v>
+      </c>
+      <c r="H5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>PJa</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v>PJ annually [TIMESreport capacityunit]</v>
+      </c>
+      <c r="G6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="L6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>SC_AGR</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>Agriculture sector [TIMESreport sector]</v>
+      </c>
+      <c r="H7" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>SC_COM</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>Commercial sector [TIMESreport sector]</v>
+      </c>
+      <c r="H8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>SC_ELE</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
         <v>Electricity supply sector [TIMESreport sector]</v>
       </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>130</v>
-      </c>
-      <c r="M3" t="s">
-        <v>103</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="H9" t="s">
+        <v>115</v>
+      </c>
+      <c r="L9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>SC_IND</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>Industry sector [TIMESreport sector]</v>
+      </c>
+      <c r="H10" t="s">
         <v>110</v>
       </c>
-      <c r="F4" t="str">
-        <f t="shared" ref="F4:F17" si="0">L4</f>
-        <v>TR_IND</v>
-      </c>
-      <c r="G4" t="str">
-        <f t="shared" ref="G4:G17" si="1">M4&amp;" [TIMESreport "&amp;N4&amp;"]"</f>
-        <v>Industry sector [TIMESreport sector]</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" t="s">
-        <v>131</v>
-      </c>
-      <c r="M4" t="s">
-        <v>104</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="L10" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" t="str">
+      <c r="E11" t="str">
         <f t="shared" si="0"/>
-        <v>TR_MIN</v>
-      </c>
-      <c r="G5" t="str">
+        <v>SC_MIN</v>
+      </c>
+      <c r="F11" t="str">
         <f t="shared" si="1"/>
         <v>Mining technologies [TIMESreport sector]</v>
       </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" t="s">
-        <v>132</v>
-      </c>
-      <c r="M5" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="E12" t="str">
         <f t="shared" si="0"/>
-        <v>TR_TRD</v>
-      </c>
-      <c r="G6" t="str">
+        <v>SC_REF</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v>Refinery  [TIMESreport sector]</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v>SC_RES</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v>Residential sector [TIMESreport sector]</v>
+      </c>
+      <c r="H13" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v>SC_TRA</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="1"/>
+        <v>Transport sector [TIMESreport sector]</v>
+      </c>
+      <c r="H14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="0"/>
+        <v>SC_TRD</v>
+      </c>
+      <c r="F15" t="str">
         <f t="shared" si="1"/>
         <v>Trade technologies [TIMESreport sector]</v>
       </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" t="s">
-        <v>133</v>
-      </c>
-      <c r="M6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="H15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L15" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="E16" t="str">
         <f t="shared" si="0"/>
-        <v>TR_REF</v>
-      </c>
-      <c r="G7" t="str">
-        <f t="shared" si="1"/>
-        <v>Refinery  [TIMESreport sector]</v>
-      </c>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" t="s">
-        <v>134</v>
-      </c>
-      <c r="M7" t="s">
-        <v>91</v>
-      </c>
-      <c r="N7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_AGR</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" si="1"/>
-        <v>Agriculture sector [TIMESreport sector]</v>
-      </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M8" t="s">
-        <v>95</v>
-      </c>
-      <c r="N8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_COM</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="1"/>
-        <v>Commercial sector [TIMESreport sector]</v>
-      </c>
-      <c r="H9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" t="s">
-        <v>13</v>
-      </c>
-      <c r="L9" t="s">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s">
-        <v>100</v>
-      </c>
-      <c r="N9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_RES</v>
-      </c>
-      <c r="G10" t="str">
-        <f t="shared" si="1"/>
-        <v>Residential sector [TIMESreport sector]</v>
-      </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" t="s">
-        <v>137</v>
-      </c>
-      <c r="M10" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_TRA</v>
-      </c>
-      <c r="G11" t="str">
-        <f t="shared" si="1"/>
-        <v>Transport sector [TIMESreport sector]</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" t="s">
-        <v>138</v>
-      </c>
-      <c r="M11" t="s">
-        <v>102</v>
-      </c>
-      <c r="N11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_TRM</v>
-      </c>
-      <c r="G12" t="str">
+        <v>SC_TRM</v>
+      </c>
+      <c r="F16" t="str">
         <f t="shared" si="1"/>
         <v>Transmission of electricity and gas [TIMESreport sector]</v>
       </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" t="s">
-        <v>139</v>
-      </c>
-      <c r="M12" t="s">
-        <v>108</v>
-      </c>
-      <c r="N12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="H16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>244</v>
+      </c>
+      <c r="B17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" ref="E17" si="2">A17</f>
+        <v>SR_AGR</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" ref="F17" si="3">B17&amp;" [TIMESreport "&amp;C17&amp;"]"</f>
+        <v>Agricultural demand [TIMESreport service]</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="L17" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v>SR_APP</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="1"/>
+        <v>Appliances [TIMESreport service]</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="L18" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v>SR_IRS</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="1"/>
+        <v>Industrial IronSteel Demand [TIMESreport service]</v>
+      </c>
+      <c r="G19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L19" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v>SR_IND</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="1"/>
+        <v>Industry Demand [TIMESreport service]</v>
+      </c>
+      <c r="G20" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" t="s">
+        <v>262</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v>SR_OTH</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="1"/>
+        <v>Other demands [TIMESreport service]</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="L21" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v>SR_RHT</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="1"/>
+        <v>Room heat [TIMESreport service]</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v>SR_TRC</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="1"/>
+        <v>Cars [TIMESreport service]</v>
+      </c>
+      <c r="G23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="L23" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>249</v>
+      </c>
+      <c r="B24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v>SR_TRP</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="1"/>
+        <v>Public transport [TIMESreport service]</v>
+      </c>
+      <c r="G24" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="L24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_AGR</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="1"/>
+        <v>Agriculture [TIMESreport subsector]</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_BIO</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="1"/>
+        <v>Domestic biomass supply [TIMESreport subsector]</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="K26" s="5"/>
+      <c r="L26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_CHP</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="1"/>
+        <v>Combined heat and power plant [TIMESreport subsector]</v>
+      </c>
+      <c r="G27" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" t="s">
+        <v>115</v>
+      </c>
+      <c r="L27" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_COA</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="1"/>
+        <v>Coal supply [TIMESreport subsector]</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K28" s="5"/>
+      <c r="L28" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_COM</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="1"/>
+        <v>Commercial [TIMESreport subsector]</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_ELC</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="1"/>
+        <v>Electricity trade [TIMESreport subsector]</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="5"/>
+      <c r="L30" t="s">
+        <v>13</v>
+      </c>
+      <c r="M30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_ELE</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="1"/>
+        <v>Power plants [TIMESreport subsector]</v>
+      </c>
+      <c r="G31" t="s">
         <v>14</v>
       </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" t="str">
+      <c r="H31" t="s">
+        <v>115</v>
+      </c>
+      <c r="L31" t="s">
+        <v>13</v>
+      </c>
+      <c r="M31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" t="str">
         <f t="shared" si="0"/>
-        <v>TR_PP_FOSSIL</v>
-      </c>
-      <c r="G13" t="str">
+        <v>SS_GAS</v>
+      </c>
+      <c r="F32" t="str">
         <f t="shared" si="1"/>
-        <v>Fossile power plants [TIMESreport techgroup]</v>
-      </c>
-      <c r="H13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13" t="s">
+        <v>Natural gas supply [TIMESreport subsector]</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="K32" s="5"/>
+      <c r="L32" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_HPL</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="1"/>
+        <v>Heating plant [TIMESreport subsector]</v>
+      </c>
+      <c r="G33" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" t="s">
+        <v>115</v>
+      </c>
+      <c r="L33" t="s">
+        <v>13</v>
+      </c>
+      <c r="M33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_IRO</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="1"/>
+        <v>Industrial Iron [TIMESreport subsector]</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="L34" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>263</v>
+      </c>
+      <c r="B35" t="s">
+        <v>264</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_IND</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="1"/>
+        <v>Industry other [TIMESreport subsector]</v>
+      </c>
+      <c r="H35" t="s">
+        <v>262</v>
+      </c>
+      <c r="L35" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>179</v>
+      </c>
+      <c r="B36" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="0"/>
+        <v>SS_NUC</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="1"/>
+        <v>Mining nuclear fuel supply [TIMESreport subsector]</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" s="5"/>
+      <c r="L36" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" t="s">
+        <v>214</v>
+      </c>
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" ref="E37:E56" si="4">A37</f>
+        <v>SS_OIL</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" ref="F37:F55" si="5">B37&amp;" [TIMESreport "&amp;C37&amp;"]"</f>
+        <v>Oil supply [TIMESreport subsector]</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="K37" s="5"/>
+      <c r="L37" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_ORE</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="5"/>
+        <v>Industrial Ore [TIMESreport subsector]</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L38" t="s">
+        <v>13</v>
+      </c>
+      <c r="M38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39" t="s">
+        <v>219</v>
+      </c>
+      <c r="C39" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_OXY</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="5"/>
+        <v>Oxygen supply  [TIMESreport subsector]</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="K39" s="5"/>
+      <c r="L39" t="s">
+        <v>13</v>
+      </c>
+      <c r="M39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_REF</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="5"/>
+        <v>Oil refinary [TIMESreport subsector]</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K40" s="5"/>
+      <c r="L40" t="s">
+        <v>13</v>
+      </c>
+      <c r="M40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_RES</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="5"/>
+        <v>Residential [TIMESreport subsector]</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="L41" t="s">
+        <v>13</v>
+      </c>
+      <c r="M41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>173</v>
+      </c>
+      <c r="B42" t="s">
+        <v>217</v>
+      </c>
+      <c r="C42" t="s">
+        <v>121</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_REW</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="5"/>
+        <v>Renewable energy supply [TIMESreport subsector]</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K42" s="5"/>
+      <c r="L42" t="s">
+        <v>13</v>
+      </c>
+      <c r="M42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_SIN</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="5"/>
+        <v>Industrial Sinter [TIMESreport subsector]</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="L43" t="s">
+        <v>13</v>
+      </c>
+      <c r="M43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" t="s">
         <v>159</v>
       </c>
-      <c r="M13" t="s">
-        <v>140</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_STE</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="5"/>
+        <v>Industrial Steel [TIMESreport subsector]</v>
+      </c>
+      <c r="H44" t="s">
+        <v>158</v>
+      </c>
+      <c r="L44" t="s">
+        <v>13</v>
+      </c>
+      <c r="M44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>203</v>
+      </c>
+      <c r="B45" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_TRC</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="5"/>
+        <v>Private transport [TIMESreport subsector]</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="L45" t="s">
+        <v>13</v>
+      </c>
+      <c r="M45" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>209</v>
+      </c>
+      <c r="B46" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_TRME</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="5"/>
+        <v>Electricity transmission [TIMESreport subsector]</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="L46" t="s">
+        <v>13</v>
+      </c>
+      <c r="M46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_TRMG</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="5"/>
+        <v>Gas transmission [TIMESreport subsector]</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="L47" t="s">
+        <v>13</v>
+      </c>
+      <c r="M47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="4"/>
+        <v>SS_TRP</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="5"/>
+        <v>Public transport [TIMESreport subsector]</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="L48" t="s">
+        <v>13</v>
+      </c>
+      <c r="M48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E49" t="str">
+        <f t="shared" si="4"/>
+        <v>TG_BIO</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="5"/>
+        <v>Biomass [TIMESreport techgroup]</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="L49" t="s">
+        <v>13</v>
+      </c>
+      <c r="M49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="4"/>
+        <v>TG_ELC</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="5"/>
+        <v>Electricity [TIMESreport techgroup]</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J50" t="s">
+        <v>149</v>
+      </c>
+      <c r="L50" t="s">
+        <v>13</v>
+      </c>
+      <c r="M50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>228</v>
+      </c>
+      <c r="B51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" t="s">
+        <v>122</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="4"/>
+        <v>TG_GAS</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="5"/>
+        <v>Gas [TIMESreport techgroup]</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" t="s">
+        <v>13</v>
+      </c>
+      <c r="M51" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>225</v>
+      </c>
+      <c r="B52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" t="s">
+        <v>122</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" si="4"/>
+        <v>TG_NUC</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="5"/>
+        <v>Nuclear [TIMESreport techgroup]</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="J52" t="s">
         <v>57</v>
       </c>
-      <c r="F14" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_PP_NUCLEAR</v>
-      </c>
-      <c r="G14" t="str">
-        <f t="shared" si="1"/>
-        <v>Nuclear power plants [TIMESreport techgroup]</v>
-      </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" t="s">
-        <v>13</v>
-      </c>
-      <c r="L14" t="s">
-        <v>160</v>
-      </c>
-      <c r="M14" t="s">
-        <v>141</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="L52" t="s">
+        <v>13</v>
+      </c>
+      <c r="M52" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_PP_RENEW</v>
-      </c>
-      <c r="G15" t="str">
-        <f t="shared" si="1"/>
-        <v>Renewable power plant [TIMESreport techgroup]</v>
-      </c>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" t="s">
-        <v>161</v>
-      </c>
-      <c r="M15" t="s">
-        <v>142</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="E53" t="str">
+        <f t="shared" si="4"/>
+        <v>TG_OIL</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="5"/>
+        <v>Oil [TIMESreport techgroup]</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J53" s="5"/>
+      <c r="L53" t="s">
+        <v>13</v>
+      </c>
+      <c r="M53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F16" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_ES_STEEL</v>
-      </c>
-      <c r="G16" t="str">
-        <f t="shared" si="1"/>
-        <v>Steel service [TIMESreport service]</v>
-      </c>
-      <c r="H16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" t="s">
-        <v>13</v>
-      </c>
-      <c r="L16" t="s">
-        <v>146</v>
-      </c>
-      <c r="M16" t="s">
-        <v>145</v>
-      </c>
-      <c r="N16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" t="s">
-        <v>155</v>
-      </c>
-      <c r="F17" t="str">
-        <f t="shared" si="0"/>
-        <v>TR_ES_OTH</v>
-      </c>
-      <c r="G17" t="str">
-        <f t="shared" si="1"/>
-        <v>Other [TIMESreport service]</v>
-      </c>
-      <c r="H17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" t="s">
-        <v>13</v>
-      </c>
-      <c r="L17" t="s">
-        <v>152</v>
-      </c>
-      <c r="M17" t="s">
-        <v>149</v>
-      </c>
-      <c r="N17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" t="str">
-        <f t="shared" ref="F18:F20" si="2">L18</f>
-        <v>TR_ES_SP</v>
-      </c>
-      <c r="G18" t="str">
-        <f t="shared" ref="G18:G20" si="3">M18&amp;" [TIMESreport "&amp;N18&amp;"]"</f>
-        <v>Space heating [TIMESreport service]</v>
-      </c>
-      <c r="H18" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" t="s">
-        <v>13</v>
-      </c>
-      <c r="L18" t="s">
-        <v>154</v>
-      </c>
-      <c r="M18" t="s">
-        <v>147</v>
-      </c>
-      <c r="N18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" t="s">
-        <v>151</v>
-      </c>
-      <c r="F19" t="str">
-        <f t="shared" si="2"/>
-        <v>TR_ES_APP</v>
-      </c>
-      <c r="G19" t="str">
-        <f t="shared" si="3"/>
-        <v>Appliances [TIMESreport service]</v>
-      </c>
-      <c r="H19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" t="s">
-        <v>13</v>
-      </c>
-      <c r="L19" t="s">
-        <v>153</v>
-      </c>
-      <c r="M19" t="s">
-        <v>148</v>
-      </c>
-      <c r="N19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" t="s">
-        <v>178</v>
-      </c>
-      <c r="F20" t="str">
-        <f t="shared" si="2"/>
-        <v>TR_ES_TR</v>
-      </c>
-      <c r="G20" t="str">
-        <f t="shared" si="3"/>
-        <v>Transport [TIMESreport service]</v>
-      </c>
-      <c r="H20" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" t="s">
-        <v>13</v>
-      </c>
-      <c r="L20" t="s">
-        <v>176</v>
-      </c>
-      <c r="M20" t="s">
-        <v>177</v>
-      </c>
-      <c r="N20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>157</v>
-      </c>
-      <c r="F21" t="str">
-        <f t="shared" ref="F21:F22" si="4">L21</f>
-        <v>TR_STEEL</v>
-      </c>
-      <c r="G21" t="str">
-        <f t="shared" ref="G21:G22" si="5">M21&amp;" [TIMESreport "&amp;N21&amp;"]"</f>
-        <v>Iron&amp;Stell [TIMESreport subsector]</v>
-      </c>
-      <c r="H21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" t="s">
-        <v>13</v>
-      </c>
-      <c r="L21" t="s">
-        <v>158</v>
-      </c>
-      <c r="M21" t="s">
-        <v>156</v>
-      </c>
-      <c r="N21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" t="s">
-        <v>172</v>
-      </c>
-      <c r="F22" t="str">
+      <c r="E54" t="str">
         <f t="shared" si="4"/>
-        <v>TR_TRAPUB</v>
-      </c>
-      <c r="G22" t="str">
+        <v>TG_REW</v>
+      </c>
+      <c r="F54" t="str">
         <f t="shared" si="5"/>
-        <v>Public Transport [TIMESreport subsector]</v>
-      </c>
-      <c r="H22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" t="s">
-        <v>13</v>
-      </c>
-      <c r="L22" t="s">
-        <v>170</v>
-      </c>
-      <c r="M22" t="s">
-        <v>171</v>
-      </c>
-      <c r="N22" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" t="str">
-        <f t="shared" ref="F23" si="6">L23</f>
-        <v>TR_TRACAR</v>
-      </c>
-      <c r="G23" t="str">
-        <f t="shared" ref="G23" si="7">M23&amp;" [TIMESreport "&amp;N23&amp;"]"</f>
-        <v>Car transport [TIMESreport subsector]</v>
-      </c>
-      <c r="H23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" t="s">
-        <v>13</v>
-      </c>
-      <c r="L23" t="s">
-        <v>175</v>
-      </c>
-      <c r="M23" t="s">
-        <v>174</v>
-      </c>
-      <c r="N23" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F24" t="str">
-        <f t="shared" ref="F24:F27" si="8">L24</f>
-        <v>Mt-y</v>
-      </c>
-      <c r="G24" t="str">
-        <f t="shared" ref="G24:G26" si="9">M24&amp;" [TIMESreport "&amp;N24&amp;"]"</f>
-        <v>Million ton a year [TIMESreport capacityunit]</v>
-      </c>
-      <c r="H24" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" t="s">
-        <v>13</v>
-      </c>
-      <c r="L24" t="s">
-        <v>162</v>
-      </c>
-      <c r="M24" t="s">
-        <v>163</v>
-      </c>
-      <c r="N24" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>184</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" t="str">
-        <f t="shared" si="8"/>
-        <v>PJa</v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="9"/>
-        <v>PJ annually [TIMESreport capacityunit]</v>
-      </c>
-      <c r="H25" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" t="s">
-        <v>13</v>
-      </c>
-      <c r="L25" t="s">
-        <v>180</v>
-      </c>
-      <c r="M25" t="s">
-        <v>181</v>
-      </c>
-      <c r="N25" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>130</v>
-      </c>
-      <c r="F26" t="str">
-        <f t="shared" si="8"/>
-        <v>GW</v>
-      </c>
-      <c r="G26" t="str">
-        <f t="shared" si="9"/>
-        <v>GW [TIMESreport capacityunit]</v>
-      </c>
-      <c r="H26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" t="s">
-        <v>182</v>
-      </c>
-      <c r="M26" t="s">
-        <v>182</v>
-      </c>
-      <c r="N26" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>138</v>
-      </c>
-      <c r="F27" t="str">
-        <f t="shared" si="8"/>
-        <v>000_Units</v>
-      </c>
-      <c r="G27" t="str">
-        <f t="shared" ref="G27" si="10">M27&amp;" [TIMESreport "&amp;N27&amp;"]"</f>
-        <v>1000 units [TIMESreport capacityunit]</v>
-      </c>
-      <c r="H27" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" t="s">
-        <v>13</v>
-      </c>
-      <c r="L27" t="s">
-        <v>185</v>
-      </c>
-      <c r="M27" t="s">
-        <v>186</v>
-      </c>
-      <c r="N27" t="s">
-        <v>179</v>
+        <v>Renewable [TIMESreport techgroup]</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="L54" t="s">
+        <v>13</v>
+      </c>
+      <c r="M54" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>250</v>
+      </c>
+      <c r="B55" t="s">
+        <v>251</v>
+      </c>
+      <c r="C55" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="4"/>
+        <v>TG_COA</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="5"/>
+        <v>Coal  [TIMESreport techgroup]</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
+        <v>13</v>
+      </c>
+      <c r="M55" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>266</v>
+      </c>
+      <c r="B56" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" t="s">
+        <v>122</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="4"/>
+        <v>TG_DMD</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" ref="F56" si="6">B56&amp;" [TIMESreport "&amp;C56&amp;"]"</f>
+        <v>Demand Technology [TIMESreport techgroup]</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J56" t="s">
+        <v>15</v>
+      </c>
+      <c r="L56" t="s">
+        <v>13</v>
+      </c>
+      <c r="M56" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Sets-DemoModels.xlsx
+++ b/Sets-DemoModels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kristoffer\DemoS_012_timesreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7684F212-534F-45FA-80FD-869BDB4EC69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5EE5C6-7976-4D18-BFC5-8FF89B71C653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="2970" windowWidth="25395" windowHeight="9195" activeTab="3" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" activeTab="2" xr2:uid="{008F860A-1793-4F78-8899-BE3F7B7A437A}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -308,7 +308,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="263">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -565,18 +565,9 @@
     <t>NRG_SOLID</t>
   </si>
   <si>
-    <t>MINING</t>
-  </si>
-  <si>
     <t>Mining technologies</t>
   </si>
   <si>
-    <t>EXP*,IMP*</t>
-  </si>
-  <si>
-    <t>TRADE</t>
-  </si>
-  <si>
     <t>Trade technologies</t>
   </si>
   <si>
@@ -586,36 +577,21 @@
     <t xml:space="preserve">Refinery </t>
   </si>
   <si>
-    <t>REFINERY</t>
-  </si>
-  <si>
     <t>A*</t>
   </si>
   <si>
-    <t>AGRICULTURE</t>
-  </si>
-  <si>
     <t>Agriculture sector</t>
   </si>
   <si>
     <t>C*</t>
   </si>
   <si>
-    <t>COMMERCIAL</t>
-  </si>
-  <si>
-    <t>RESIDENTIAL</t>
-  </si>
-  <si>
     <t>Residential sector</t>
   </si>
   <si>
     <t>Commercial sector</t>
   </si>
   <si>
-    <t>TRANSPORT</t>
-  </si>
-  <si>
     <t>Transport sector</t>
   </si>
   <si>
@@ -625,15 +601,9 @@
     <t>Industry sector</t>
   </si>
   <si>
-    <t>INDUSTRY</t>
-  </si>
-  <si>
     <t>T*,-TU*,-TB*</t>
   </si>
   <si>
-    <t>TRANSMISSION</t>
-  </si>
-  <si>
     <t>Transmission of electricity and gas</t>
   </si>
   <si>
@@ -646,12 +616,6 @@
     <t>R*,-REF*</t>
   </si>
   <si>
-    <t>ELECTRICITY</t>
-  </si>
-  <si>
-    <t>Sector definition for TIMESreport</t>
-  </si>
-  <si>
     <t>Default set in DemoModel</t>
   </si>
   <si>
@@ -713,9 +677,6 @@
   </si>
   <si>
     <t>Million ton a year</t>
-  </si>
-  <si>
-    <t>TFM_Psets</t>
   </si>
   <si>
     <t>EXP*,IMP*,-IMP*Z</t>
@@ -1686,23 +1647,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD03DB1-DD55-4548-B86E-1F92E13CF8ED}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="65.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="56" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1728,7 +1689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>72</v>
       </c>
@@ -1745,7 +1706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1759,7 +1720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1776,7 +1737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -1790,7 +1751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>79</v>
       </c>
@@ -1804,7 +1765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>81</v>
       </c>
@@ -1818,7 +1779,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>83</v>
       </c>
@@ -1839,19 +1800,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06336B7-5D6A-48EE-B122-F085391548AD}">
-  <dimension ref="A1:J116"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1883,256 +1844,256 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
@@ -2142,21 +2103,19 @@
         <v>13</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
@@ -2166,21 +2125,21 @@
         <v>13</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="F15" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
@@ -2190,21 +2149,21 @@
         <v>13</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F16" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
@@ -2214,21 +2173,21 @@
         <v>13</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F17" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
@@ -2238,21 +2197,21 @@
         <v>13</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
@@ -2262,21 +2221,21 @@
         <v>13</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="F19" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
@@ -2286,21 +2245,19 @@
         <v>13</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
@@ -2310,21 +2267,19 @@
         <v>13</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
@@ -2334,21 +2289,21 @@
         <v>13</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
@@ -2358,21 +2313,21 @@
         <v>13</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
@@ -2382,19 +2337,21 @@
         <v>13</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
@@ -2404,21 +2361,21 @@
         <v>13</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2" t="s">
@@ -2428,21 +2385,21 @@
         <v>13</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="D26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
@@ -2452,21 +2409,21 @@
         <v>13</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2" t="s">
@@ -2476,21 +2433,21 @@
         <v>13</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2" t="s">
@@ -2500,21 +2457,19 @@
         <v>13</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
@@ -2524,19 +2479,21 @@
         <v>13</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
@@ -2546,19 +2503,21 @@
         <v>13</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2" t="s">
@@ -2568,21 +2527,21 @@
         <v>13</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2" t="s">
@@ -2592,21 +2551,21 @@
         <v>13</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
@@ -2616,21 +2575,21 @@
         <v>13</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
@@ -2640,21 +2599,21 @@
         <v>13</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="D35" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
@@ -2664,21 +2623,21 @@
         <v>13</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
@@ -2688,21 +2647,21 @@
         <v>13</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="D37" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2" t="s">
@@ -2712,21 +2671,21 @@
         <v>13</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="D38" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2" t="s">
@@ -2736,19 +2695,21 @@
         <v>13</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="D39" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2" t="s">
@@ -2758,21 +2719,19 @@
         <v>13</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
@@ -2782,21 +2741,21 @@
         <v>13</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="F41" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2" t="s">
@@ -2806,21 +2765,21 @@
         <v>13</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F42" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
@@ -2830,21 +2789,21 @@
         <v>13</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F43" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2" t="s">
@@ -2854,21 +2813,21 @@
         <v>13</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="F44" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2" t="s">
@@ -2878,21 +2837,21 @@
         <v>13</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="F45" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2" t="s">
@@ -2902,21 +2861,19 @@
         <v>13</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2" t="s">
@@ -2926,21 +2883,19 @@
         <v>13</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2" t="s">
@@ -2950,21 +2905,21 @@
         <v>13</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B48" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C48" s="2"/>
-      <c r="D48" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
@@ -2974,21 +2929,21 @@
         <v>13</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
@@ -2998,19 +2953,21 @@
         <v>13</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="D50" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
@@ -3020,21 +2977,21 @@
         <v>13</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
@@ -3044,21 +3001,21 @@
         <v>13</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="D52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2" t="s">
@@ -3068,21 +3025,21 @@
         <v>13</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2" t="s">
@@ -3092,21 +3049,21 @@
         <v>13</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2" t="s">
@@ -3116,21 +3073,19 @@
         <v>13</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2" t="s">
@@ -3140,19 +3095,21 @@
         <v>13</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
+      <c r="D56" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2" t="s">
@@ -3162,19 +3119,21 @@
         <v>13</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
+      <c r="D57" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2" t="s">
@@ -3184,21 +3143,21 @@
         <v>13</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="D58" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2" t="s">
@@ -3208,21 +3167,21 @@
         <v>13</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2" t="s">
@@ -3232,21 +3191,21 @@
         <v>13</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2" t="s">
@@ -3256,21 +3215,21 @@
         <v>13</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B61" s="2"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
+      <c r="D61" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2" t="s">
@@ -3280,21 +3239,21 @@
         <v>13</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2" t="s">
@@ -3304,21 +3263,21 @@
         <v>13</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
+      <c r="D63" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2" t="s">
@@ -3328,21 +3287,21 @@
         <v>13</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="D64" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2" t="s">
@@ -3352,19 +3311,21 @@
         <v>13</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
+      <c r="D65" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2" t="s">
@@ -3374,21 +3335,19 @@
         <v>13</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2" t="s">
@@ -3398,21 +3357,21 @@
         <v>13</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="F67" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2" t="s">
@@ -3422,21 +3381,21 @@
         <v>13</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F68" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
@@ -3446,21 +3405,21 @@
         <v>13</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F69" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2" t="s">
@@ -3470,21 +3429,21 @@
         <v>13</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="F70" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2" t="s">
@@ -3494,21 +3453,21 @@
         <v>13</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="F71" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2" t="s">
@@ -3518,21 +3477,19 @@
         <v>13</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A72" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B72" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C72" s="2"/>
-      <c r="D72" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2" t="s">
@@ -3542,21 +3499,19 @@
         <v>13</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A73" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B73" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C73" s="2"/>
-      <c r="D73" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2" t="s">
@@ -3566,21 +3521,21 @@
         <v>13</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B74" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C74" s="2"/>
-      <c r="D74" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2" t="s">
@@ -3590,21 +3545,21 @@
         <v>13</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
@@ -3614,19 +3569,21 @@
         <v>13</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
+      <c r="D76" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2" t="s">
@@ -3636,21 +3593,21 @@
         <v>13</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2" t="s">
@@ -3660,21 +3617,21 @@
         <v>13</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="D78" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2" t="s">
@@ -3684,21 +3641,21 @@
         <v>13</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2" t="s">
@@ -3708,21 +3665,21 @@
         <v>13</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2" t="s">
@@ -3732,21 +3689,19 @@
         <v>13</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A81" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B81" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2" t="s">
@@ -3756,19 +3711,21 @@
         <v>13</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
+      <c r="D82" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2" t="s">
@@ -3778,19 +3735,21 @@
         <v>13</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+      <c r="D83" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2" t="s">
@@ -3800,21 +3759,21 @@
         <v>13</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
+      <c r="D84" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2" t="s">
@@ -3824,21 +3783,21 @@
         <v>13</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2" t="s">
@@ -3848,21 +3807,21 @@
         <v>13</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2" t="s">
@@ -3872,21 +3831,21 @@
         <v>13</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B87" s="2"/>
       <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
+      <c r="D87" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2" t="s">
@@ -3896,21 +3855,21 @@
         <v>13</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2" t="s">
@@ -3920,21 +3879,21 @@
         <v>13</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="B89" s="2"/>
       <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+      <c r="D89" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2" t="s">
@@ -3944,21 +3903,21 @@
         <v>13</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B90" s="2"/>
       <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+      <c r="D90" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2" t="s">
@@ -3968,19 +3927,21 @@
         <v>13</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
+      <c r="D91" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2" t="s">
@@ -3990,21 +3951,19 @@
         <v>13</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A92" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B92" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C92" s="2"/>
-      <c r="D92" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2" t="s">
@@ -4014,21 +3973,21 @@
         <v>13</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="F93" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2" t="s">
@@ -4038,21 +3997,21 @@
         <v>13</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
-      <c r="D94" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F94" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2" t="s">
@@ -4062,21 +4021,21 @@
         <v>13</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
-      <c r="D95" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F95" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2" t="s">
@@ -4086,21 +4045,21 @@
         <v>13</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
-      <c r="D96" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="F96" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2" t="s">
@@ -4110,21 +4069,21 @@
         <v>13</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
-      <c r="D97" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="F97" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2" t="s">
@@ -4134,21 +4093,19 @@
         <v>13</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A98" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B98" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C98" s="2"/>
-      <c r="D98" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2" t="s">
@@ -4158,21 +4115,19 @@
         <v>13</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A99" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B99" s="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C99" s="2"/>
-      <c r="D99" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2" t="s">
@@ -4182,21 +4137,21 @@
         <v>13</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B100" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C100" s="2"/>
-      <c r="D100" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2" t="s">
@@ -4206,21 +4161,21 @@
         <v>13</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2" t="s">
@@ -4230,19 +4185,21 @@
         <v>13</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="D102" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2" t="s">
@@ -4252,21 +4209,21 @@
         <v>13</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2" t="s">
@@ -4276,21 +4233,21 @@
         <v>13</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="D104" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2" t="s">
@@ -4300,21 +4257,21 @@
         <v>13</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B105" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="E105" s="2"/>
       <c r="F105" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2" t="s">
@@ -4324,21 +4281,21 @@
         <v>13</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B106" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="E106" s="2"/>
       <c r="F106" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2" t="s">
@@ -4348,243 +4305,7 @@
         <v>13</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A107" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A110" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A111" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A112" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A113" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A114" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A115" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A116" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4598,32 +4319,32 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -4650,15 +4371,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E11" si="0">A3</f>
@@ -4669,10 +4390,10 @@
         <v>Electricity [TIMESreport comgroup]</v>
       </c>
       <c r="G3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="J3" t="s">
         <v>13</v>
@@ -4681,15 +4402,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -4700,7 +4421,7 @@
         <v>Gas [TIMESreport comgroup]</v>
       </c>
       <c r="G4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
@@ -4712,15 +4433,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -4731,7 +4452,7 @@
         <v>Nuclear [TIMESreport comgroup]</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -4743,15 +4464,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -4762,7 +4483,7 @@
         <v>Oil [TIMESreport comgroup]</v>
       </c>
       <c r="G6" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H6" t="s">
         <v>79</v>
@@ -4774,15 +4495,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -4793,10 +4514,10 @@
         <v>Renewable [TIMESreport comgroup]</v>
       </c>
       <c r="G7" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="J7" t="s">
         <v>13</v>
@@ -4805,15 +4526,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -4824,7 +4545,7 @@
         <v>Coal [TIMESreport comgroup]</v>
       </c>
       <c r="G8" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4836,15 +4557,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -4855,10 +4576,10 @@
         <v>Biomass [TIMESreport comgroup]</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="J9" t="s">
         <v>13</v>
@@ -4867,15 +4588,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>272</v>
-      </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -4886,10 +4607,10 @@
         <v>GHG-emission [TIMESreport comgroup]</v>
       </c>
       <c r="G10" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="H10" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="J10" t="s">
         <v>13</v>
@@ -4898,15 +4619,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -4917,10 +4638,10 @@
         <v>Demand commodity [TIMESreport comgroup]</v>
       </c>
       <c r="G11" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="H11" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="J11" t="s">
         <v>13</v>
@@ -4941,34 +4662,34 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:N56"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="143.26953125" customWidth="1"/>
-    <col min="10" max="10" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="143.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -5001,15 +4722,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E36" si="0">A3</f>
@@ -5020,7 +4741,7 @@
         <v>1000 units [TIMESreport capacityunit]</v>
       </c>
       <c r="H3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L3" t="s">
         <v>13</v>
@@ -5029,15 +4750,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -5048,7 +4769,7 @@
         <v>GW [TIMESreport capacityunit]</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
@@ -5057,15 +4778,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E5" t="str">
         <f>A5</f>
@@ -5076,7 +4797,7 @@
         <v>Million ton a year [TIMESreport capacityunit]</v>
       </c>
       <c r="H5" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -5085,15 +4806,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -5104,10 +4825,10 @@
         <v>PJ annually [TIMESreport capacityunit]</v>
       </c>
       <c r="G6" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="L6" t="s">
         <v>13</v>
@@ -5116,15 +4837,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -5135,24 +4856,24 @@
         <v>Agriculture sector [TIMESreport sector]</v>
       </c>
       <c r="H7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" t="s">
         <v>93</v>
       </c>
-      <c r="L7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" t="s">
-        <v>100</v>
-      </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -5163,7 +4884,7 @@
         <v>Commercial sector [TIMESreport sector]</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s">
         <v>13</v>
@@ -5172,15 +4893,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -5191,7 +4912,7 @@
         <v>Electricity supply sector [TIMESreport sector]</v>
       </c>
       <c r="H9" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s">
         <v>13</v>
@@ -5200,15 +4921,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -5219,7 +4940,7 @@
         <v>Industry sector [TIMESreport sector]</v>
       </c>
       <c r="H10" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L10" t="s">
         <v>13</v>
@@ -5228,15 +4949,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -5256,15 +4977,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -5275,7 +4996,7 @@
         <v>Refinery  [TIMESreport sector]</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L12" t="s">
         <v>13</v>
@@ -5284,15 +5005,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -5303,7 +5024,7 @@
         <v>Residential sector [TIMESreport sector]</v>
       </c>
       <c r="H13" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="L13" t="s">
         <v>13</v>
@@ -5312,15 +5033,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -5331,7 +5052,7 @@
         <v>Transport sector [TIMESreport sector]</v>
       </c>
       <c r="H14" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L14" t="s">
         <v>13</v>
@@ -5340,15 +5061,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -5359,7 +5080,7 @@
         <v>Trade technologies [TIMESreport sector]</v>
       </c>
       <c r="H15" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s">
         <v>13</v>
@@ -5368,15 +5089,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -5387,7 +5108,7 @@
         <v>Transmission of electricity and gas [TIMESreport sector]</v>
       </c>
       <c r="H16" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L16" t="s">
         <v>13</v>
@@ -5396,15 +5117,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" ref="E17" si="2">A17</f>
@@ -5415,7 +5136,7 @@
         <v>Agricultural demand [TIMESreport service]</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s">
         <v>13</v>
@@ -5424,15 +5145,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -5443,7 +5164,7 @@
         <v>Appliances [TIMESreport service]</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="L18" t="s">
         <v>13</v>
@@ -5452,15 +5173,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -5471,13 +5192,13 @@
         <v>Industrial IronSteel Demand [TIMESreport service]</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="L19" t="s">
         <v>13</v>
@@ -5486,15 +5207,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -5505,10 +5226,10 @@
         <v>Industry Demand [TIMESreport service]</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H20" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" t="s">
@@ -5518,15 +5239,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -5537,7 +5258,7 @@
         <v>Other demands [TIMESreport service]</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s">
         <v>13</v>
@@ -5546,15 +5267,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -5565,7 +5286,7 @@
         <v>Room heat [TIMESreport service]</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="L22" t="s">
         <v>13</v>
@@ -5574,15 +5295,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
@@ -5593,10 +5314,10 @@
         <v>Cars [TIMESreport service]</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s">
         <v>13</v>
@@ -5605,15 +5326,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E24" t="str">
         <f t="shared" si="0"/>
@@ -5624,10 +5345,10 @@
         <v>Public transport [TIMESreport service]</v>
       </c>
       <c r="G24" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="L24" t="s">
         <v>13</v>
@@ -5636,15 +5357,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -5655,7 +5376,7 @@
         <v>Agriculture [TIMESreport subsector]</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" t="s">
@@ -5665,15 +5386,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -5684,7 +5405,7 @@
         <v>Domestic biomass supply [TIMESreport subsector]</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" t="s">
@@ -5694,15 +5415,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -5713,10 +5434,10 @@
         <v>Combined heat and power plant [TIMESreport subsector]</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="H27" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s">
         <v>13</v>
@@ -5725,15 +5446,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -5744,7 +5465,7 @@
         <v>Coal supply [TIMESreport subsector]</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" t="s">
@@ -5754,15 +5475,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -5773,7 +5494,7 @@
         <v>Commercial [TIMESreport subsector]</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L29" t="s">
         <v>13</v>
@@ -5782,15 +5503,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E30" t="str">
         <f t="shared" si="0"/>
@@ -5801,7 +5522,7 @@
         <v>Electricity trade [TIMESreport subsector]</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" t="s">
@@ -5811,15 +5532,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E31" t="str">
         <f t="shared" si="0"/>
@@ -5833,7 +5554,7 @@
         <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s">
         <v>13</v>
@@ -5842,15 +5563,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E32" t="str">
         <f t="shared" si="0"/>
@@ -5861,7 +5582,7 @@
         <v>Natural gas supply [TIMESreport subsector]</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" t="s">
@@ -5871,15 +5592,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E33" t="str">
         <f t="shared" si="0"/>
@@ -5890,10 +5611,10 @@
         <v>Heating plant [TIMESreport subsector]</v>
       </c>
       <c r="G33" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="H33" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s">
         <v>13</v>
@@ -5902,15 +5623,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E34" t="str">
         <f t="shared" si="0"/>
@@ -5921,7 +5642,7 @@
         <v>Industrial Iron [TIMESreport subsector]</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="L34" t="s">
         <v>13</v>
@@ -5930,15 +5651,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B35" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E35" t="str">
         <f t="shared" si="0"/>
@@ -5949,7 +5670,7 @@
         <v>Industry other [TIMESreport subsector]</v>
       </c>
       <c r="H35" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="L35" t="s">
         <v>13</v>
@@ -5958,15 +5679,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E36" t="str">
         <f t="shared" si="0"/>
@@ -5977,7 +5698,7 @@
         <v>Mining nuclear fuel supply [TIMESreport subsector]</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" t="s">
@@ -5987,15 +5708,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E37" t="str">
         <f t="shared" ref="E37:E56" si="4">A37</f>
@@ -6006,7 +5727,7 @@
         <v>Oil supply [TIMESreport subsector]</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" t="s">
@@ -6016,15 +5737,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E38" t="str">
         <f t="shared" si="4"/>
@@ -6035,7 +5756,7 @@
         <v>Industrial Ore [TIMESreport subsector]</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L38" t="s">
         <v>13</v>
@@ -6044,15 +5765,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E39" t="str">
         <f t="shared" si="4"/>
@@ -6063,7 +5784,7 @@
         <v>Oxygen supply  [TIMESreport subsector]</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" t="s">
@@ -6073,15 +5794,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E40" t="str">
         <f t="shared" si="4"/>
@@ -6092,7 +5813,7 @@
         <v>Oil refinary [TIMESreport subsector]</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" t="s">
@@ -6102,15 +5823,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E41" t="str">
         <f t="shared" si="4"/>
@@ -6121,7 +5842,7 @@
         <v>Residential [TIMESreport subsector]</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="L41" t="s">
         <v>13</v>
@@ -6130,15 +5851,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B42" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E42" t="str">
         <f t="shared" si="4"/>
@@ -6149,7 +5870,7 @@
         <v>Renewable energy supply [TIMESreport subsector]</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="K42" s="5"/>
       <c r="L42" t="s">
@@ -6159,15 +5880,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E43" t="str">
         <f t="shared" si="4"/>
@@ -6178,7 +5899,7 @@
         <v>Industrial Sinter [TIMESreport subsector]</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="L43" t="s">
         <v>13</v>
@@ -6187,15 +5908,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E44" t="str">
         <f t="shared" si="4"/>
@@ -6206,7 +5927,7 @@
         <v>Industrial Steel [TIMESreport subsector]</v>
       </c>
       <c r="H44" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="L44" t="s">
         <v>13</v>
@@ -6215,15 +5936,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E45" t="str">
         <f t="shared" si="4"/>
@@ -6234,7 +5955,7 @@
         <v>Private transport [TIMESreport subsector]</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="L45" t="s">
         <v>13</v>
@@ -6243,15 +5964,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E46" t="str">
         <f t="shared" si="4"/>
@@ -6262,7 +5983,7 @@
         <v>Electricity transmission [TIMESreport subsector]</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="L46" t="s">
         <v>13</v>
@@ -6271,15 +5992,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E47" t="str">
         <f t="shared" si="4"/>
@@ -6290,7 +6011,7 @@
         <v>Gas transmission [TIMESreport subsector]</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="L47" t="s">
         <v>13</v>
@@ -6299,15 +6020,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E48" t="str">
         <f t="shared" si="4"/>
@@ -6318,7 +6039,7 @@
         <v>Public transport [TIMESreport subsector]</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="L48" t="s">
         <v>13</v>
@@ -6327,15 +6048,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E49" t="str">
         <f t="shared" si="4"/>
@@ -6346,7 +6067,7 @@
         <v>Biomass [TIMESreport techgroup]</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="L49" t="s">
         <v>13</v>
@@ -6355,15 +6076,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E50" t="str">
         <f t="shared" si="4"/>
@@ -6377,7 +6098,7 @@
         <v>72</v>
       </c>
       <c r="J50" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s">
         <v>13</v>
@@ -6386,15 +6107,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E51" t="str">
         <f t="shared" si="4"/>
@@ -6414,15 +6135,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E52" t="str">
         <f t="shared" si="4"/>
@@ -6433,7 +6154,7 @@
         <v>Nuclear [TIMESreport techgroup]</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="J52" t="s">
         <v>57</v>
@@ -6445,15 +6166,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E53" t="str">
         <f t="shared" si="4"/>
@@ -6464,7 +6185,7 @@
         <v>Oil [TIMESreport techgroup]</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="J53" s="5"/>
       <c r="L53" t="s">
@@ -6474,15 +6195,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="4"/>
@@ -6493,7 +6214,7 @@
         <v>Renewable [TIMESreport techgroup]</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="L54" t="s">
         <v>13</v>
@@ -6502,15 +6223,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="B55" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E55" t="str">
         <f t="shared" si="4"/>
@@ -6533,15 +6254,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B56" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E56" t="str">
         <f t="shared" si="4"/>
@@ -6552,7 +6273,7 @@
         <v>Demand Technology [TIMESreport techgroup]</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="J56" t="s">
         <v>15</v>
